--- a/AAII_Financials/Yearly/ILMN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ILMN_YR_FIN.xlsx
@@ -3029,10 +3029,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>377000</v>
+        <v>394000</v>
       </c>
       <c r="E59" s="3">
-        <v>361000</v>
+        <v>379000</v>
       </c>
       <c r="F59" s="3">
         <v>891000</v>
